--- a/data/trans_orig/P36BPD14_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023</t>
+          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37277</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55332</t>
+          <t>54382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>79253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98222</t>
+          <t>98711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139151</t>
+          <t>139852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256320</t>
+          <t>258529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>313142</t>
+          <t>315664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267090</t>
+          <t>268984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307609</t>
+          <t>310754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541441</t>
+          <t>538813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>610007</t>
+          <t>611119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>268202</t>
+          <t>265616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>323060</t>
+          <t>323131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>296982</t>
+          <t>297986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>338310</t>
+          <t>339582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>579145</t>
+          <t>575199</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>646624</t>
+          <t>643504</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120228</t>
+          <t>120842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93136</t>
+          <t>93488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109381</t>
+          <t>109337</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201743</t>
+          <t>200941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236737</t>
+          <t>216272</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>571791</t>
+          <t>570652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>442271</t>
+          <t>444155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>496758</t>
+          <t>496261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>575419</t>
+          <t>605576</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1043103</t>
+          <t>1044569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>512424</t>
+          <t>512549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>911632</t>
+          <t>932959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>377473</t>
+          <t>380315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>432977</t>
+          <t>430208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>913055</t>
+          <t>911598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1477204</t>
+          <t>1427428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>55024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93487</t>
+          <t>93131</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>49105</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133224</t>
+          <t>134108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113609</t>
+          <t>108542</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>206843</t>
+          <t>207086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264288</t>
+          <t>266118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324319</t>
+          <t>324134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135774</t>
+          <t>160554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>414796</t>
+          <t>412296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>370365</t>
+          <t>398456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>707312</t>
+          <t>710041</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306405</t>
+          <t>306453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370323</t>
+          <t>366376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393721</t>
+          <t>393641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746929</t>
+          <t>716108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728908</t>
+          <t>732956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1150152</t>
+          <t>1126478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>63756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102775</t>
+          <t>104096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75539</t>
+          <t>73946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113019</t>
+          <t>111604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148503</t>
+          <t>147552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203274</t>
+          <t>203989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319909</t>
+          <t>322638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386049</t>
+          <t>385387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>310096</t>
+          <t>308418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424743</t>
+          <t>425532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>657223</t>
+          <t>654874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>794421</t>
+          <t>791430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458438</t>
+          <t>457190</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>523118</t>
+          <t>522585</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>569627</t>
+          <t>570320</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>711425</t>
+          <t>706410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1045904</t>
+          <t>1047668</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1205733</t>
+          <t>1202475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229983</t>
+          <t>225319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>336286</t>
+          <t>336566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,82 +2569,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>334765</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>278361</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>375598</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>624924</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>547038</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>692037</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>9,75%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>334765</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>273694</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>372622</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>809</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>624924</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>534808</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>686337</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>8,81%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1093686</t>
+          <t>1105412</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1500316</t>
+          <t>1514335</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1182551</t>
+          <t>1186477</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1570080</t>
+          <t>1581264</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2433520</t>
+          <t>2463622</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3033221</t>
+          <t>3038526</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1636312</t>
+          <t>1625113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2111407</t>
+          <t>2120096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1722984</t>
+          <t>1715160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2193738</t>
+          <t>2185959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3403865</t>
+          <t>3400038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4114980</t>
+          <t>4064753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD14_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>65673</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>48162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>87528</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>66279</t>
+          <t>77448</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79253</t>
+          <t>95888</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>117056</t>
+          <t>143122</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98711</t>
+          <t>121588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139852</t>
+          <t>169580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>286701</t>
+          <t>307693</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258529</t>
+          <t>280231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315664</t>
+          <t>337485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>288868</t>
+          <t>313594</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268984</t>
+          <t>292341</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310754</t>
+          <t>337942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>575569</t>
+          <t>621287</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>538813</t>
+          <t>584567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611119</t>
+          <t>658729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>293481</t>
+          <t>311141</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265616</t>
+          <t>280788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>323131</t>
+          <t>338044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>317732</t>
+          <t>338370</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>297986</t>
+          <t>314006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>339582</t>
+          <t>361819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>611212</t>
+          <t>649510</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>575199</t>
+          <t>613216</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>643504</t>
+          <t>686666</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>630958</t>
+          <t>684507</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>630958</t>
+          <t>684507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>630958</t>
+          <t>684507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>672879</t>
+          <t>729412</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>672879</t>
+          <t>729412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>672879</t>
+          <t>729412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1303837</t>
+          <t>1413919</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1303837</t>
+          <t>1413919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1303837</t>
+          <t>1413919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84902</t>
+          <t>90244</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>71657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120842</t>
+          <t>115368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77092</t>
+          <t>88260</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62516</t>
+          <t>72411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93488</t>
+          <t>106601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>161994</t>
+          <t>178504</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109337</t>
+          <t>153212</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200941</t>
+          <t>205819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>443729</t>
+          <t>490604</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>216272</t>
+          <t>454340</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>570652</t>
+          <t>527830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>469187</t>
+          <t>518114</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>444155</t>
+          <t>491477</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>496261</t>
+          <t>549714</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>912916</t>
+          <t>1008718</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>605576</t>
+          <t>960803</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1044569</t>
+          <t>1054951</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>660152</t>
+          <t>463714</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>512549</t>
+          <t>428415</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>932959</t>
+          <t>502000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>406334</t>
+          <t>458512</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>380315</t>
+          <t>428725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>430208</t>
+          <t>486644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1066486</t>
+          <t>922226</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>911598</t>
+          <t>875445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1427428</t>
+          <t>972575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1188783</t>
+          <t>1044562</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1188783</t>
+          <t>1044562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1188783</t>
+          <t>1044562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>952613</t>
+          <t>1064886</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>952613</t>
+          <t>1064886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>952613</t>
+          <t>1064886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2141396</t>
+          <t>2109448</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2141396</t>
+          <t>2109448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2141396</t>
+          <t>2109448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>92657</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55024</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93131</t>
+          <t>120267</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97084</t>
+          <t>110154</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49105</t>
+          <t>93489</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134108</t>
+          <t>130130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>170808</t>
+          <t>202811</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108542</t>
+          <t>175875</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>207086</t>
+          <t>235147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>292861</t>
+          <t>330115</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266118</t>
+          <t>297854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>324134</t>
+          <t>361276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>309158</t>
+          <t>325040</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160554</t>
+          <t>299614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>412296</t>
+          <t>351736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>602019</t>
+          <t>655155</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398456</t>
+          <t>611666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>710041</t>
+          <t>694391</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>337212</t>
+          <t>379379</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306453</t>
+          <t>348926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366376</t>
+          <t>412159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>522209</t>
+          <t>371941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>393641</t>
+          <t>346460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>716108</t>
+          <t>397867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>859420</t>
+          <t>751320</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>732956</t>
+          <t>712596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1126478</t>
+          <t>795873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>703797</t>
+          <t>802151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>703797</t>
+          <t>802151</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>703797</t>
+          <t>802151</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>928451</t>
+          <t>807135</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>928451</t>
+          <t>807135</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>928451</t>
+          <t>807135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1632247</t>
+          <t>1609286</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1632247</t>
+          <t>1609286</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1632247</t>
+          <t>1609286</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80756</t>
+          <t>82640</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>64625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104096</t>
+          <t>103995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94310</t>
+          <t>104481</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73946</t>
+          <t>88164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111604</t>
+          <t>124389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>175066</t>
+          <t>187121</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147552</t>
+          <t>162712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203989</t>
+          <t>213663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>352782</t>
+          <t>389590</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322638</t>
+          <t>357476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>385387</t>
+          <t>420432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>387619</t>
+          <t>431494</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>308418</t>
+          <t>403387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>425532</t>
+          <t>462756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>740401</t>
+          <t>821084</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>654874</t>
+          <t>778917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>791430</t>
+          <t>862104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>490387</t>
+          <t>515094</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>457190</t>
+          <t>480970</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>522585</t>
+          <t>547662</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>613003</t>
+          <t>583066</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>570320</t>
+          <t>551592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>706410</t>
+          <t>613195</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103389</t>
+          <t>1098161</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1047668</t>
+          <t>1056304</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1202475</t>
+          <t>1140380</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>923925</t>
+          <t>987324</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>923925</t>
+          <t>987324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>923925</t>
+          <t>987324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2018857</t>
+          <t>2106366</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2018857</t>
+          <t>2106366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2018857</t>
+          <t>2106366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>290159</t>
+          <t>331214</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225319</t>
+          <t>293997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>336566</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>334765</t>
+          <t>380343</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>278361</t>
+          <t>348575</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375598</t>
+          <t>416155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>624924</t>
+          <t>711557</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547038</t>
+          <t>659977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>692037</t>
+          <t>767367</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1376073</t>
+          <t>1518003</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1105412</t>
+          <t>1457276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1514335</t>
+          <t>1581529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1454832</t>
+          <t>1588242</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1186477</t>
+          <t>1536739</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1581264</t>
+          <t>1642008</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2830905</t>
+          <t>3106244</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2463622</t>
+          <t>3025277</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3038526</t>
+          <t>3194034</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1781231</t>
+          <t>1669328</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1625113</t>
+          <t>1600993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2120096</t>
+          <t>1730392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1859278</t>
+          <t>1751889</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1715160</t>
+          <t>1699075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2185959</t>
+          <t>1808235</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3640508</t>
+          <t>3421217</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3400038</t>
+          <t>3334668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4064753</t>
+          <t>3499752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3447463</t>
+          <t>3518545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3648875</t>
+          <t>3720474</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7096338</t>
+          <t>7239019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
